--- a/data/raw_fake/pedidos_cd.xlsx
+++ b/data/raw_fake/pedidos_cd.xlsx
@@ -454,12 +454,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID100000</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ID100000</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -528,12 +528,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ID100001</t>
+          <t>ID859396</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ID100001</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,12 +575,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID100002</t>
+          <t>ID517026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ID100002</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ID100003</t>
+          <t>ID985785</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ID100003</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ID100004</t>
+          <t>ID183493</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ID100004</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -708,12 +708,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID100005</t>
+          <t>ID408532</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ID100005</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -751,12 +751,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID100006</t>
+          <t>ID550233</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ID100006</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -798,12 +798,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID100007</t>
+          <t>ID544606</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ID100007</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID100008</t>
+          <t>ID250175</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ID100008</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -888,12 +888,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID100009</t>
+          <t>ID385443</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ID100009</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -931,12 +931,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID100010</t>
+          <t>ID291148</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ID100010</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -978,12 +978,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID100011</t>
+          <t>ID762465</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ID100011</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID100012</t>
+          <t>ID376803</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ID100012</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1068,12 +1068,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID100013</t>
+          <t>ID756027</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ID100013</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID100014</t>
+          <t>ID517712</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ID100014</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1158,12 +1158,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ID100015</t>
+          <t>ID513700</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ID100015</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1205,12 +1205,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ID100016</t>
+          <t>ID565860</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ID100016</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID100017</t>
+          <t>ID422120</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ID100017</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1299,12 +1299,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ID100018</t>
+          <t>ID969375</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ID100018</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ID100019</t>
+          <t>ID398052</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ID100019</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1385,12 +1385,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ID100020</t>
+          <t>ID982937</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ID100020</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ID100021</t>
+          <t>ID798018</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ID100021</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1479,12 +1479,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ID100022</t>
+          <t>ID359114</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ID100022</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ID100023</t>
+          <t>ID657112</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ID100023</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ID100024</t>
+          <t>ID262330</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ID100024</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1616,12 +1616,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ID100025</t>
+          <t>ID628935</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ID100025</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1663,12 +1663,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ID100026</t>
+          <t>ID204678</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ID100026</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1710,12 +1710,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ID100027</t>
+          <t>ID244481</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ID100027</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1757,12 +1757,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ID100028</t>
+          <t>ID671497</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ID100028</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ID100029</t>
+          <t>ID643426</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ID100029</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1847,12 +1847,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ID100030</t>
+          <t>ID451801</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ID100030</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1894,12 +1894,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ID100031</t>
+          <t>ID138219</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ID100031</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ID100032</t>
+          <t>ID272292</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ID100032</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1980,12 +1980,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ID100033</t>
+          <t>ID434078</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ID100033</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ID100034</t>
+          <t>ID472857</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ID100034</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2074,12 +2074,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ID100035</t>
+          <t>ID813071</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ID100035</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2121,12 +2121,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ID100036</t>
+          <t>ID103822</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ID100036</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2168,12 +2168,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ID100037</t>
+          <t>ID815088</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ID100037</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2215,12 +2215,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ID100038</t>
+          <t>ID987713</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ID100038</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2258,12 +2258,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ID100039</t>
+          <t>ID990955</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ID100039</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2305,12 +2305,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ID100040</t>
+          <t>ID927987</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ID100040</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2348,12 +2348,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ID100041</t>
+          <t>ID661485</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ID100041</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2395,12 +2395,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ID100042</t>
+          <t>ID180901</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ID100042</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ID100043</t>
+          <t>ID428369</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ID100043</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2489,12 +2489,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ID100044</t>
+          <t>ID937174</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ID100044</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2536,12 +2536,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ID100045</t>
+          <t>ID268619</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ID100045</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2583,12 +2583,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ID100046</t>
+          <t>ID703815</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ID100046</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2626,12 +2626,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ID100047</t>
+          <t>ID614245</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ID100047</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2669,12 +2669,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ID100048</t>
+          <t>ID811435</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ID100048</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2712,12 +2712,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ID100049</t>
+          <t>ID804355</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ID100049</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2759,12 +2759,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ID100050</t>
+          <t>ID270174</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ID100050</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ID100051</t>
+          <t>ID807918</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ID100051</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2849,12 +2849,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ID100052</t>
+          <t>ID351673</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ID100052</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2896,12 +2896,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ID100053</t>
+          <t>ID295377</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ID100053</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2943,12 +2943,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ID100054</t>
+          <t>ID889474</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ID100054</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2990,12 +2990,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ID100055</t>
+          <t>ID158775</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ID100055</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ID100056</t>
+          <t>ID884745</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ID100056</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3080,12 +3080,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ID100057</t>
+          <t>ID120190</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ID100057</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3123,12 +3123,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ID100058</t>
+          <t>ID825099</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ID100058</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ID100059</t>
+          <t>ID769428</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ID100059</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3209,12 +3209,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ID100060</t>
+          <t>ID714574</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ID100060</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ID100061</t>
+          <t>ID966216</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ID100061</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3299,12 +3299,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ID100062</t>
+          <t>ID502478</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ID100062</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3346,12 +3346,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ID100063</t>
+          <t>ID853174</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ID100063</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ID100064</t>
+          <t>ID122338</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ID100064</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3436,12 +3436,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ID100065</t>
+          <t>ID817850</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ID100065</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3483,12 +3483,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ID100066</t>
+          <t>ID922922</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ID100066</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3526,12 +3526,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ID100067</t>
+          <t>ID946511</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ID100067</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3573,12 +3573,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ID100068</t>
+          <t>ID764543</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ID100068</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ID100069</t>
+          <t>ID668655</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ID100069</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3667,12 +3667,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ID100070</t>
+          <t>ID834699</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ID100070</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ID100071</t>
+          <t>ID987095</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ID100071</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3761,12 +3761,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ID100072</t>
+          <t>ID327709</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ID100072</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3804,12 +3804,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ID100073</t>
+          <t>ID600995</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ID100073</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ID100074</t>
+          <t>ID954654</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ID100074</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3898,12 +3898,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ID100075</t>
+          <t>ID246726</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ID100075</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3945,12 +3945,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ID100076</t>
+          <t>ID382221</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ID100076</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ID100077</t>
+          <t>ID517467</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ID100077</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4035,12 +4035,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ID100078</t>
+          <t>ID773670</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ID100078</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4082,12 +4082,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ID100079</t>
+          <t>ID321811</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ID100079</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4129,12 +4129,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ID100080</t>
+          <t>ID235942</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ID100080</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4176,12 +4176,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ID100081</t>
+          <t>ID951638</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ID100081</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4223,12 +4223,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ID100082</t>
+          <t>ID511343</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ID100082</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4270,12 +4270,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ID100083</t>
+          <t>ID799075</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ID100083</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4313,12 +4313,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ID100084</t>
+          <t>ID630604</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ID100084</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4360,12 +4360,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ID100085</t>
+          <t>ID855930</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ID100085</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4403,12 +4403,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ID100086</t>
+          <t>ID765553</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ID100086</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4446,12 +4446,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ID100087</t>
+          <t>ID908623</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ID100087</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4493,12 +4493,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ID100088</t>
+          <t>ID379672</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ID100088</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4536,12 +4536,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ID100089</t>
+          <t>ID331086</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ID100089</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4579,12 +4579,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ID100090</t>
+          <t>ID441634</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ID100090</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4622,12 +4622,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ID100091</t>
+          <t>ID344845</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ID100091</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4665,12 +4665,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ID100092</t>
+          <t>ID138293</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ID100092</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4708,12 +4708,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ID100093</t>
+          <t>ID683024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ID100093</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4755,12 +4755,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ID100094</t>
+          <t>ID383397</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ID100094</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4798,12 +4798,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ID100095</t>
+          <t>ID414134</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ID100095</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4845,12 +4845,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ID100096</t>
+          <t>ID417173</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ID100096</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4892,12 +4892,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ID100097</t>
+          <t>ID967341</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ID100097</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4935,12 +4935,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ID100098</t>
+          <t>ID533221</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ID100098</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ID100099</t>
+          <t>ID136300</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ID100099</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5025,12 +5025,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ID100100</t>
+          <t>ID684330</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ID100100</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5072,12 +5072,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ID100101</t>
+          <t>ID309663</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ID100101</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5119,12 +5119,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ID100102</t>
+          <t>ID765204</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ID100102</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5166,12 +5166,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ID100103</t>
+          <t>ID302880</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ID100103</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5213,12 +5213,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ID100104</t>
+          <t>ID101595</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ID100104</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5256,12 +5256,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ID100105</t>
+          <t>ID396888</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ID100105</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5303,12 +5303,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ID100106</t>
+          <t>ID940808</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ID100106</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5346,12 +5346,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ID100107</t>
+          <t>ID342986</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ID100107</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ID100108</t>
+          <t>ID658014</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ID100108</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5440,12 +5440,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ID100109</t>
+          <t>ID815656</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ID100109</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5487,12 +5487,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ID100110</t>
+          <t>ID358924</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ID100110</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5534,12 +5534,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ID100111</t>
+          <t>ID887613</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ID100111</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5581,12 +5581,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ID100112</t>
+          <t>ID726780</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ID100112</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5628,12 +5628,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ID100113</t>
+          <t>ID463161</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ID100113</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ID100114</t>
+          <t>ID289364</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ID100114</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5718,12 +5718,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ID100115</t>
+          <t>ID642815</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ID100115</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5765,12 +5765,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ID100116</t>
+          <t>ID328166</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ID100116</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5812,12 +5812,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ID100117</t>
+          <t>ID260706</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ID100117</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5859,12 +5859,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ID100118</t>
+          <t>ID146355</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ID100118</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5902,12 +5902,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ID100119</t>
+          <t>ID217821</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ID100119</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5949,12 +5949,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ID100120</t>
+          <t>ID699639</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ID100120</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5996,12 +5996,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ID100121</t>
+          <t>ID780219</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ID100121</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6043,12 +6043,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ID100122</t>
+          <t>ID756795</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ID100122</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6090,12 +6090,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ID100123</t>
+          <t>ID895692</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ID100123</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6137,12 +6137,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ID100124</t>
+          <t>ID918816</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ID100124</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6184,12 +6184,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ID100125</t>
+          <t>ID483713</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ID100125</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6231,12 +6231,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ID100126</t>
+          <t>ID567045</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ID100126</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6278,12 +6278,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ID100127</t>
+          <t>ID299207</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ID100127</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6321,12 +6321,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ID100128</t>
+          <t>ID907594</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ID100128</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6364,12 +6364,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ID100129</t>
+          <t>ID713207</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ID100129</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6411,12 +6411,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ID100130</t>
+          <t>ID669116</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ID100130</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6454,12 +6454,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ID100131</t>
+          <t>ID400627</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ID100131</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6497,12 +6497,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ID100132</t>
+          <t>ID759316</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ID100132</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6540,12 +6540,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ID100133</t>
+          <t>ID587726</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ID100133</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6587,12 +6587,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ID100134</t>
+          <t>ID622333</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ID100134</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6634,12 +6634,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ID100135</t>
+          <t>ID573071</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ID100135</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6681,12 +6681,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ID100136</t>
+          <t>ID423667</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ID100136</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6724,12 +6724,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ID100137</t>
+          <t>ID384636</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ID100137</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6767,12 +6767,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ID100138</t>
+          <t>ID884806</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ID100138</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6814,12 +6814,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ID100139</t>
+          <t>ID930420</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ID100139</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6861,12 +6861,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ID100140</t>
+          <t>ID393107</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ID100140</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6908,12 +6908,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ID100141</t>
+          <t>ID935809</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ID100141</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6955,12 +6955,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ID100142</t>
+          <t>ID474046</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ID100142</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7002,12 +7002,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ID100143</t>
+          <t>ID746889</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ID100143</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7049,12 +7049,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ID100144</t>
+          <t>ID908242</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ID100144</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7092,12 +7092,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ID100145</t>
+          <t>ID419815</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ID100145</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7139,12 +7139,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ID100146</t>
+          <t>ID937774</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ID100146</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7186,12 +7186,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ID100147</t>
+          <t>ID339907</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ID100147</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7233,12 +7233,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ID100148</t>
+          <t>ID897316</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ID100148</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7280,12 +7280,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ID100149</t>
+          <t>ID337259</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ID100149</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7327,12 +7327,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ID100150</t>
+          <t>ID218915</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ID100150</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7374,12 +7374,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ID100151</t>
+          <t>ID922459</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ID100151</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7417,12 +7417,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ID100152</t>
+          <t>ID916612</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ID100152</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ID100153</t>
+          <t>ID311034</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ID100153</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7507,12 +7507,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ID100154</t>
+          <t>ID745111</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ID100154</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7550,12 +7550,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ID100155</t>
+          <t>ID922848</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ID100155</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7597,12 +7597,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ID100156</t>
+          <t>ID348885</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ID100156</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7644,12 +7644,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ID100157</t>
+          <t>ID161188</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ID100157</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7687,12 +7687,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ID100158</t>
+          <t>ID844059</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ID100158</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7734,12 +7734,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ID100159</t>
+          <t>ID858874</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ID100159</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7777,12 +7777,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ID100160</t>
+          <t>ID738861</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ID100160</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7820,12 +7820,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ID100161</t>
+          <t>ID708945</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ID100161</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7867,12 +7867,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ID100162</t>
+          <t>ID337314</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ID100162</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7914,12 +7914,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ID100163</t>
+          <t>ID811308</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ID100163</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7961,12 +7961,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ID100164</t>
+          <t>ID443179</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ID100164</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8004,12 +8004,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ID100165</t>
+          <t>ID776260</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ID100165</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8051,12 +8051,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ID100166</t>
+          <t>ID910426</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ID100166</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8098,12 +8098,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ID100167</t>
+          <t>ID452141</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ID100167</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8145,12 +8145,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ID100168</t>
+          <t>ID199467</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ID100168</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8188,12 +8188,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ID100169</t>
+          <t>ID495495</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ID100169</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8231,12 +8231,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ID100170</t>
+          <t>ID100136</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ID100170</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8278,12 +8278,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ID100171</t>
+          <t>ID134961</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ID100171</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8325,12 +8325,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ID100172</t>
+          <t>ID454009</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ID100172</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8368,12 +8368,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ID100173</t>
+          <t>ID935915</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ID100173</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8415,12 +8415,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ID100174</t>
+          <t>ID692842</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ID100174</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8458,12 +8458,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ID100175</t>
+          <t>ID205962</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ID100175</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8505,12 +8505,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ID100176</t>
+          <t>ID155983</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ID100176</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8552,12 +8552,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ID100177</t>
+          <t>ID125330</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ID100177</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8595,12 +8595,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ID100178</t>
+          <t>ID210682</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ID100178</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8642,12 +8642,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ID100179</t>
+          <t>ID997689</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ID100179</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8689,12 +8689,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ID100180</t>
+          <t>ID755090</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ID100180</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8736,12 +8736,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ID100181</t>
+          <t>ID372776</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ID100181</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8783,12 +8783,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ID100182</t>
+          <t>ID309907</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ID100182</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8830,12 +8830,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ID100183</t>
+          <t>ID261710</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ID100183</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8877,12 +8877,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ID100184</t>
+          <t>ID656426</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ID100184</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8920,12 +8920,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ID100185</t>
+          <t>ID957219</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ID100185</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8967,12 +8967,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ID100186</t>
+          <t>ID202526</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ID100186</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9014,12 +9014,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ID100187</t>
+          <t>ID564450</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ID100187</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9061,12 +9061,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ID100188</t>
+          <t>ID605137</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ID100188</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9108,12 +9108,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ID100189</t>
+          <t>ID192846</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ID100189</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -9155,12 +9155,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ID100190</t>
+          <t>ID124452</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ID100190</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9202,12 +9202,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ID100191</t>
+          <t>ID642320</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ID100191</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9245,12 +9245,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ID100192</t>
+          <t>ID421851</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ID100192</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9288,12 +9288,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ID100193</t>
+          <t>ID285417</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ID100193</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9335,12 +9335,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ID100194</t>
+          <t>ID631844</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ID100194</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9378,12 +9378,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ID100195</t>
+          <t>ID345922</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ID100195</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9425,12 +9425,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ID100196</t>
+          <t>ID810575</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ID100196</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9472,12 +9472,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ID100197</t>
+          <t>ID781082</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ID100197</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9515,12 +9515,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ID100198</t>
+          <t>ID303184</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ID100198</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9562,12 +9562,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ID100199</t>
+          <t>ID785693</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ID100199</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9609,12 +9609,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ID100200</t>
+          <t>ID185427</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ID100200</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9656,12 +9656,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ID100201</t>
+          <t>ID437930</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ID100201</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9703,12 +9703,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ID100202</t>
+          <t>ID702329</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ID100202</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9746,12 +9746,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ID100203</t>
+          <t>ID407509</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ID100203</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9789,12 +9789,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ID100204</t>
+          <t>ID173587</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ID100204</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9832,12 +9832,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ID100205</t>
+          <t>ID997513</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ID100205</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9879,12 +9879,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ID100206</t>
+          <t>ID289738</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ID100206</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9922,12 +9922,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ID100207</t>
+          <t>ID934908</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ID100207</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9969,12 +9969,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ID100208</t>
+          <t>ID564380</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ID100208</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10016,12 +10016,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ID100209</t>
+          <t>ID470155</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ID100209</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -10059,12 +10059,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ID100210</t>
+          <t>ID346183</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ID100210</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10106,12 +10106,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ID100211</t>
+          <t>ID954190</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ID100211</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10153,12 +10153,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ID100212</t>
+          <t>ID469593</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ID100212</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -10196,12 +10196,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ID100213</t>
+          <t>ID149001</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ID100213</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -10243,12 +10243,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ID100214</t>
+          <t>ID585543</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ID100214</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10286,12 +10286,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ID100215</t>
+          <t>ID815467</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ID100215</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10333,12 +10333,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ID100216</t>
+          <t>ID254958</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ID100216</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10380,12 +10380,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ID100217</t>
+          <t>ID897483</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ID100217</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10427,12 +10427,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ID100218</t>
+          <t>ID628018</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ID100218</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -10474,12 +10474,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ID100219</t>
+          <t>ID504544</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ID100219</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10521,12 +10521,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ID100220</t>
+          <t>ID480901</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ID100220</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10568,12 +10568,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ID100221</t>
+          <t>ID139487</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ID100221</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10615,12 +10615,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ID100222</t>
+          <t>ID482232</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ID100222</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10662,12 +10662,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ID100223</t>
+          <t>ID659975</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ID100223</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10709,12 +10709,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ID100224</t>
+          <t>ID116374</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ID100224</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10756,12 +10756,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ID100225</t>
+          <t>ID885612</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ID100225</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10803,12 +10803,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ID100226</t>
+          <t>ID227951</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ID100226</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10850,12 +10850,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ID100227</t>
+          <t>ID120034</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ID100227</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10897,12 +10897,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ID100228</t>
+          <t>ID375105</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ID100228</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10944,12 +10944,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ID100229</t>
+          <t>ID400827</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ID100229</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10987,12 +10987,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ID100230</t>
+          <t>ID481788</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ID100230</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -11034,12 +11034,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ID100231</t>
+          <t>ID756104</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ID100231</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -11081,12 +11081,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ID100232</t>
+          <t>ID877336</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ID100232</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -11128,12 +11128,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ID100233</t>
+          <t>ID217470</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ID100233</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -11171,12 +11171,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ID100234</t>
+          <t>ID443660</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ID100234</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -11214,12 +11214,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ID100235</t>
+          <t>ID952630</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ID100235</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -11257,12 +11257,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ID100236</t>
+          <t>ID208660</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ID100236</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -11304,12 +11304,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ID100237</t>
+          <t>ID533067</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ID100237</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -11351,12 +11351,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ID100238</t>
+          <t>ID308695</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ID100238</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -11394,12 +11394,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ID100239</t>
+          <t>ID344543</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ID100239</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -11437,12 +11437,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ID100240</t>
+          <t>ID773563</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ID100240</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -11484,12 +11484,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ID100241</t>
+          <t>ID188996</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ID100241</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -11531,12 +11531,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ID100242</t>
+          <t>ID398534</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ID100242</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -11574,12 +11574,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ID100243</t>
+          <t>ID370586</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ID100243</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -11621,12 +11621,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ID100244</t>
+          <t>ID163535</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ID100244</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11668,12 +11668,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ID100245</t>
+          <t>ID810460</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ID100245</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11715,12 +11715,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ID100246</t>
+          <t>ID301036</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ID100246</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -11758,12 +11758,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ID100247</t>
+          <t>ID841965</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ID100247</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11805,12 +11805,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ID100248</t>
+          <t>ID726442</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ID100248</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11852,12 +11852,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ID100249</t>
+          <t>ID251404</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ID100249</t>
+          <t>ID866769</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -11895,12 +11895,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ID100250</t>
+          <t>ID886535</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ID100250</t>
+          <t>ID463451</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
